--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260707.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260707.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>8,464,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>8,464,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>26,819,000</t>
+          <t>38,623,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>38,623,000</t>
+          <t>26,819,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
